--- a/www/flightdata/xlsx/eoss-383.xlsx
+++ b/www/flightdata/xlsx/eoss-383.xlsx
@@ -3513,7 +3513,7 @@
         <v>29367.48</v>
       </c>
       <c r="I2">
-        <v>724</v>
+        <v>449</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
